--- a/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
+++ b/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-india\InputData\hydgn\HPEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\hydgn\HPEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144CF766-F142-4FDB-B3C8-5736800C38EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25815" windowHeight="11970"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -23,17 +24,28 @@
     <definedName name="hours_per_year">'Conversion Factors'!$A$1</definedName>
     <definedName name="usd_year_conv">'Conversion Factors'!$A$5</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t>HPEC Hydrogen Production Equipment CapEx</t>
   </si>
@@ -274,16 +286,16 @@
     <t>OpEx Cost ($/BTU)</t>
   </si>
   <si>
-    <t>India:US cost adjustment</t>
-  </si>
-  <si>
-    <t>see "scaling-factors.xlsx in the InputData folder for source information.</t>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -363,7 +375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -383,16 +395,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -673,24 +678,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="45.86328125" customWidth="1"/>
+    <col min="2" max="2" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -698,245 +703,230 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" s="7">
         <v>2014</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A57">
-        <v>0.50596615326007366</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1"/>
-    <hyperlink ref="B39" r:id="rId2"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -944,17 +934,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="25.3984375" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" customWidth="1"/>
-    <col min="5" max="5" width="10.1328125" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" customWidth="1"/>
+    <col min="1" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -974,7 +964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -994,7 +984,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>10</v>
       </c>
@@ -1011,7 +1001,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -1028,7 +1018,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -1046,7 +1036,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1066,7 +1056,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -1083,7 +1073,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -1100,7 +1090,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>17</v>
@@ -1118,7 +1108,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1138,7 +1128,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>10</v>
       </c>
@@ -1155,7 +1145,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1172,7 +1162,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>17</v>
@@ -1190,8 +1180,8 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1211,11 +1201,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1">
         <f>24*365</f>
         <v>8760</v>
@@ -1224,7 +1214,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3412.14</v>
       </c>
@@ -1232,7 +1222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.91400000000000003</v>
       </c>
@@ -1246,17 +1236,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AI8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1328125" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
@@ -1299,7 +1289,7 @@
       <c r="N1" s="9">
         <v>2029</v>
       </c>
-      <c r="O1" s="13">
+      <c r="O1" s="12">
         <v>2030</v>
       </c>
       <c r="P1" s="10">
@@ -1363,708 +1353,990 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.3924487595491251E-5</v>
-      </c>
-      <c r="C2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,C$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.3686462166508471E-5</v>
-      </c>
-      <c r="D2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,D$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.3448436737525744E-5</v>
-      </c>
-      <c r="E2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,E$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.3210411308542961E-5</v>
-      </c>
-      <c r="F2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,F$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.2972385879560236E-5</v>
-      </c>
-      <c r="G2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,G$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.2734360450577452E-5</v>
-      </c>
-      <c r="H2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,H$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.249633502159467E-5</v>
-      </c>
-      <c r="I2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,I$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.2258309592611945E-5</v>
-      </c>
-      <c r="J2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,J$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.2020284163629161E-5</v>
-      </c>
-      <c r="K2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,K$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.1782258734646438E-5</v>
-      </c>
-      <c r="L2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,L$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.1544233305663652E-5</v>
-      </c>
-      <c r="M2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,M$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.1306207876680928E-5</v>
-      </c>
-      <c r="N2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,N$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.1068182447698145E-5</v>
-      </c>
-      <c r="O2" s="12">
-        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,O$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.0830157018715419E-5</v>
-      </c>
-      <c r="P2" s="14">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,P$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.0636761357666929E-5</v>
-      </c>
-      <c r="Q2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,Q$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.0443365696618441E-5</v>
-      </c>
-      <c r="R2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,R$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.0249970035569952E-5</v>
-      </c>
-      <c r="S2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,S$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.0056574374521459E-5</v>
-      </c>
-      <c r="T2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,T$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>9.8631787134729705E-6</v>
-      </c>
-      <c r="U2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,U$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>9.6697830524244822E-6</v>
-      </c>
-      <c r="V2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,V$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>9.4763873913759921E-6</v>
-      </c>
-      <c r="W2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,W$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>9.2829917303275021E-6</v>
-      </c>
-      <c r="X2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,X$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>9.089596069279012E-6</v>
-      </c>
-      <c r="Y2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,Y$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>8.8962004082305237E-6</v>
-      </c>
-      <c r="Z2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,Z$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>8.7028047471820336E-6</v>
-      </c>
-      <c r="AA2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AA$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>8.5094090861335419E-6</v>
-      </c>
-      <c r="AB2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AB$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>8.3160134250850535E-6</v>
-      </c>
-      <c r="AC2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AC$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>8.1226177640365635E-6</v>
-      </c>
-      <c r="AD2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AD$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>7.9292221029880751E-6</v>
-      </c>
-      <c r="AE2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AE$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>7.7358264419395851E-6</v>
-      </c>
-      <c r="AF2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AF$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>7.5424307808910942E-6</v>
-      </c>
-      <c r="AG2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AG$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>7.3490351198426058E-6</v>
-      </c>
-      <c r="AH2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AH$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>7.1556394587941166E-6</v>
-      </c>
-      <c r="AI2" s="17">
-        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>6.9622437977456257E-6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="B2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7520591062805481E-5</v>
+      </c>
+      <c r="C2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,C$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7050153608740382E-5</v>
+      </c>
+      <c r="D2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,D$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.6579716154675392E-5</v>
+      </c>
+      <c r="E2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,E$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.6109278700610286E-5</v>
+      </c>
+      <c r="F2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,F$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.5638841246545299E-5</v>
+      </c>
+      <c r="G2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,G$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.5168403792480193E-5</v>
+      </c>
+      <c r="H2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,H$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.469796633841509E-5</v>
+      </c>
+      <c r="I2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,I$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.4227528884350103E-5</v>
+      </c>
+      <c r="J2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,J$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.3757091430284997E-5</v>
+      </c>
+      <c r="K2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,K$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.328665397622001E-5</v>
+      </c>
+      <c r="L2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,L$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.2816216522154904E-5</v>
+      </c>
+      <c r="M2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,M$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.2345779068089914E-5</v>
+      </c>
+      <c r="N2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,N$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.1875341614024811E-5</v>
+      </c>
+      <c r="O2" s="11">
+        <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,O$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.1404904159959821E-5</v>
+      </c>
+      <c r="P2" s="13">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,P$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.1022673728531968E-5</v>
+      </c>
+      <c r="Q2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,Q$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.0640443297104115E-5</v>
+      </c>
+      <c r="R2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,R$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.0258212865676262E-5</v>
+      </c>
+      <c r="S2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,S$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.9875982434248403E-5</v>
+      </c>
+      <c r="T2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,T$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.949375200282055E-5</v>
+      </c>
+      <c r="U2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,U$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.9111521571392698E-5</v>
+      </c>
+      <c r="V2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,V$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.8729291139964845E-5</v>
+      </c>
+      <c r="W2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,W$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.8347060708536989E-5</v>
+      </c>
+      <c r="X2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,X$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.7964830277109136E-5</v>
+      </c>
+      <c r="Y2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,Y$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.7582599845681283E-5</v>
+      </c>
+      <c r="Z2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,Z$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.7200369414253427E-5</v>
+      </c>
+      <c r="AA2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AA$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.6818138982825571E-5</v>
+      </c>
+      <c r="AB2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AB$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.6435908551397718E-5</v>
+      </c>
+      <c r="AC2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AC$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.6053678119969865E-5</v>
+      </c>
+      <c r="AD2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AD$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.5671447688542013E-5</v>
+      </c>
+      <c r="AE2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AE$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.5289217257114157E-5</v>
+      </c>
+      <c r="AF2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AF$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.4906986825686302E-5</v>
+      </c>
+      <c r="AG2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AG$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.4524756394258449E-5</v>
+      </c>
+      <c r="AH2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AH$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.4142525962830597E-5</v>
+      </c>
+      <c r="AI2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.3760295531402741E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="C3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,C$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="D3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,D$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="E3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,E$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="F3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,F$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="G3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,G$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="H3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,H$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="I3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,I$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="J3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,J$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="K3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,K$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="L3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,L$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="M3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,M$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="N3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,N$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="O3" s="12">
-        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,O$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="P3" s="14">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,P$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="Q3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,Q$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="R3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,R$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="S3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,S$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="T3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,T$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="U3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,U$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="V3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,V$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="W3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,W$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="X3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,X$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="Y3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,Y$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="Z3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,Z$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AA3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AA$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AB3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AB$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AC3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AC$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AD3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AD$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AE3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AE$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AF3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AF$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AG3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AG$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AH3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AH$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-      <c r="AI3" s="17">
-        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>1.4079204124330045E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="B3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="C3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,C$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="D3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,D$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="E3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,E$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="F3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,F$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="G3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,G$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="H3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,H$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="I3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,I$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="J3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,J$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="K3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,K$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="L3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,L$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="M3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,M$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="N3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,N$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="O3" s="11">
+        <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,O$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="P3" s="13">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,P$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="Q3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,Q$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="R3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,R$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="S3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,S$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="T3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,T$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="U3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,U$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="V3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,V$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="W3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,W$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="X3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,X$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="Y3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,Y$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="Z3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,Z$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AA3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AA$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AB3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AB$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AC3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AC$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AD3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AD$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AE3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AE$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AF3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AF$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AG3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AG$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AH3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AH$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AI3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="C4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,C$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="D4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,D$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="E4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,E$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="F4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,F$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="G4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,G$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="H4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,H$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="I4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,I$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="J4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,J$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="K4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,K$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="L4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,L$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="M4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,M$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="N4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,N$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="O4" s="12">
-        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,O$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="P4" s="14">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,P$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="Q4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,Q$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="R4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,R$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="S4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,S$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="T4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,T$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="U4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,U$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="V4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,V$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="W4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,W$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="X4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,X$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="Y4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,Y$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="Z4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,Z$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AA4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AA$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AB4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AB$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AC4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AC$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AD4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AD$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AE4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AE$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AF4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AF$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AG4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AG$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AH4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AH$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AI4" s="17">
-        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv*About!$A$57</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="B4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="C4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,C$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="D4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,D$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="E4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,E$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="F4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,F$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="G4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,G$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="H4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,H$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="I4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,I$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="J4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,J$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="K4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,K$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="L4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,L$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="M4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,M$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="N4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,N$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="O4" s="11">
+        <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,O$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="P4" s="13">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,P$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="Q4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,Q$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="R4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,R$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="S4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,S$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="T4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,T$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="U4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,U$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="V4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,V$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="W4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,W$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="X4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,X$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="Y4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,Y$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="Z4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,Z$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AA4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AA$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AB4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AB$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AC4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AC$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AD4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AD$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AE4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AE$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AF4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AF$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AG4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AG$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AH4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AH$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AI4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>B4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="C5" s="12">
-        <f t="shared" ref="C5:O5" si="0">C4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="D5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="E5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="F5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="G5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="H5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="K5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="L5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="M5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="N5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="O5" s="12">
-        <f t="shared" si="0"/>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="P5" s="12">
-        <f t="shared" ref="P5" si="1">P4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="Q5" s="12">
-        <f t="shared" ref="Q5" si="2">Q4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="R5" s="12">
-        <f t="shared" ref="R5" si="3">R4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="S5" s="12">
-        <f t="shared" ref="S5" si="4">S4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="T5" s="12">
-        <f t="shared" ref="T5" si="5">T4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="U5" s="12">
-        <f t="shared" ref="U5" si="6">U4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="V5" s="12">
-        <f t="shared" ref="V5" si="7">V4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="W5" s="12">
-        <f t="shared" ref="W5" si="8">W4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="X5" s="12">
-        <f t="shared" ref="X5" si="9">X4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="Y5" s="12">
-        <f t="shared" ref="Y5" si="10">Y4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="Z5" s="12">
-        <f t="shared" ref="Z5" si="11">Z4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AA5" s="12">
-        <f t="shared" ref="AA5" si="12">AA4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AB5" s="12">
-        <f t="shared" ref="AB5" si="13">AB4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AC5" s="12">
-        <f t="shared" ref="AC5" si="14">AC4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AD5" s="12">
-        <f t="shared" ref="AD5" si="15">AD4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AE5" s="12">
-        <f t="shared" ref="AE5" si="16">AE4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AF5" s="12">
-        <f t="shared" ref="AF5" si="17">AF4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AG5" s="12">
-        <f t="shared" ref="AG5" si="18">AG4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AH5" s="12">
-        <f t="shared" ref="AH5" si="19">AH4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-      <c r="AI5" s="12">
-        <f t="shared" ref="AI5" si="20">AI4</f>
-        <v>4.1309313199957377E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="C5" s="11">
+        <f t="shared" ref="C5:P5" si="0">C4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="D5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="E5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="F5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="J5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="K5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="L5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="M5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="N5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="O5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="P5" s="11">
+        <f t="shared" si="0"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="Q5" s="11">
+        <f t="shared" ref="Q5" si="1">Q4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="R5" s="11">
+        <f t="shared" ref="R5" si="2">R4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="S5" s="11">
+        <f t="shared" ref="S5" si="3">S4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="T5" s="11">
+        <f t="shared" ref="T5" si="4">T4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="U5" s="11">
+        <f t="shared" ref="U5" si="5">U4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="V5" s="11">
+        <f t="shared" ref="V5" si="6">V4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="W5" s="11">
+        <f t="shared" ref="W5" si="7">W4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="X5" s="11">
+        <f t="shared" ref="X5" si="8">X4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" ref="Y5" si="9">Y4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="Z5" s="11">
+        <f t="shared" ref="Z5" si="10">Z4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AA5" s="11">
+        <f t="shared" ref="AA5" si="11">AA4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AB5" s="11">
+        <f t="shared" ref="AB5" si="12">AB4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AC5" s="11">
+        <f t="shared" ref="AC5" si="13">AC4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AD5" s="11">
+        <f t="shared" ref="AD5" si="14">AD4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AE5" s="11">
+        <f t="shared" ref="AE5" si="15">AE4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AF5" s="11">
+        <f t="shared" ref="AF5" si="16">AF4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AG5" s="11">
+        <f t="shared" ref="AG5" si="17">AG4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AH5" s="11">
+        <f t="shared" ref="AH5" si="18">AH4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AI5" s="11">
+        <f t="shared" ref="AI5" si="19">AI4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="11">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11">
-        <f t="shared" ref="C6:R6" si="21">$B6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="11">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:R6" si="20">$B6</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" ref="S6:AI6" si="21">$B6</f>
+        <v>0</v>
+      </c>
+      <c r="T6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="E6" s="11">
+      <c r="U6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="F6" s="11">
+      <c r="V6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="G6" s="11">
+      <c r="W6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H6" s="11">
+      <c r="X6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="I6" s="11">
+      <c r="Y6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="J6" s="11">
+      <c r="Z6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="K6" s="11">
+      <c r="AA6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="AB6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="M6" s="11">
+      <c r="AC6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="N6" s="11">
+      <c r="AD6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="O6" s="11">
+      <c r="AE6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="P6" s="11">
+      <c r="AF6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="AG6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="R6" s="11">
+      <c r="AH6">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="S6" s="11">
-        <f t="shared" ref="S6:AI6" si="22">$B6</f>
-        <v>0</v>
-      </c>
-      <c r="T6" s="11">
+      <c r="AI6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="11">
+        <f>B2</f>
+        <v>2.7520591062805481E-5</v>
+      </c>
+      <c r="C7" s="11">
+        <f t="shared" ref="C7:AI7" si="22">C2</f>
+        <v>2.7050153608740382E-5</v>
+      </c>
+      <c r="D7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U6" s="11">
+        <v>2.6579716154675392E-5</v>
+      </c>
+      <c r="E7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="V6" s="11">
+        <v>2.6109278700610286E-5</v>
+      </c>
+      <c r="F7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="W6" s="11">
+        <v>2.5638841246545299E-5</v>
+      </c>
+      <c r="G7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="X6" s="11">
+        <v>2.5168403792480193E-5</v>
+      </c>
+      <c r="H7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="11">
+        <v>2.469796633841509E-5</v>
+      </c>
+      <c r="I7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="11">
+        <v>2.4227528884350103E-5</v>
+      </c>
+      <c r="J7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AA6" s="11">
+        <v>2.3757091430284997E-5</v>
+      </c>
+      <c r="K7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AB6" s="11">
+        <v>2.328665397622001E-5</v>
+      </c>
+      <c r="L7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="11">
+        <v>2.2816216522154904E-5</v>
+      </c>
+      <c r="M7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="11">
+        <v>2.2345779068089914E-5</v>
+      </c>
+      <c r="N7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AE6" s="11">
+        <v>2.1875341614024811E-5</v>
+      </c>
+      <c r="O7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AF6" s="11">
+        <v>2.1404904159959821E-5</v>
+      </c>
+      <c r="P7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AG6" s="11">
+        <v>2.1022673728531968E-5</v>
+      </c>
+      <c r="Q7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AH6" s="11">
+        <v>2.0640443297104115E-5</v>
+      </c>
+      <c r="R7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AI6" s="11">
+        <v>2.0258212865676262E-5</v>
+      </c>
+      <c r="S7" s="11">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1.9875982434248403E-5</v>
+      </c>
+      <c r="T7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.949375200282055E-5</v>
+      </c>
+      <c r="U7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.9111521571392698E-5</v>
+      </c>
+      <c r="V7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.8729291139964845E-5</v>
+      </c>
+      <c r="W7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.8347060708536989E-5</v>
+      </c>
+      <c r="X7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.7964830277109136E-5</v>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.7582599845681283E-5</v>
+      </c>
+      <c r="Z7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.7200369414253427E-5</v>
+      </c>
+      <c r="AA7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.6818138982825571E-5</v>
+      </c>
+      <c r="AB7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.6435908551397718E-5</v>
+      </c>
+      <c r="AC7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.6053678119969865E-5</v>
+      </c>
+      <c r="AD7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.5671447688542013E-5</v>
+      </c>
+      <c r="AE7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.5289217257114157E-5</v>
+      </c>
+      <c r="AF7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.4906986825686302E-5</v>
+      </c>
+      <c r="AG7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.4524756394258449E-5</v>
+      </c>
+      <c r="AH7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.4142525962830597E-5</v>
+      </c>
+      <c r="AI7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.3760295531402741E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="11">
+        <f>B3</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="C8" s="11">
+        <f t="shared" ref="C8:AI8" si="23">C3</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="D8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="E8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="F8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="H8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="I8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="J8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="K8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="L8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="N8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="O8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="P8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="Q8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="R8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="S8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="T8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="U8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="V8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="W8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="X8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="Z8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AA8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AB8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AC8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AD8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AE8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AF8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AG8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AH8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AI8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
       </c>
     </row>
   </sheetData>
@@ -2073,825 +2345,1107 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AI8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1328125" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="15">
+      <c r="B1" s="9">
         <v>2017</v>
       </c>
-      <c r="C1" s="16">
+      <c r="C1">
         <v>2018</v>
       </c>
-      <c r="D1" s="15">
+      <c r="D1" s="9">
         <v>2019</v>
       </c>
-      <c r="E1" s="16">
+      <c r="E1">
         <v>2020</v>
       </c>
-      <c r="F1" s="15">
+      <c r="F1" s="9">
         <v>2021</v>
       </c>
-      <c r="G1" s="16">
+      <c r="G1">
         <v>2022</v>
       </c>
-      <c r="H1" s="15">
+      <c r="H1" s="9">
         <v>2023</v>
       </c>
-      <c r="I1" s="16">
+      <c r="I1">
         <v>2024</v>
       </c>
-      <c r="J1" s="15">
+      <c r="J1" s="9">
         <v>2025</v>
       </c>
-      <c r="K1" s="16">
+      <c r="K1">
         <v>2026</v>
       </c>
-      <c r="L1" s="15">
+      <c r="L1" s="9">
         <v>2027</v>
       </c>
-      <c r="M1" s="16">
+      <c r="M1">
         <v>2028</v>
       </c>
-      <c r="N1" s="15">
+      <c r="N1" s="9">
         <v>2029</v>
       </c>
-      <c r="O1" s="16">
+      <c r="O1">
         <v>2030</v>
       </c>
-      <c r="P1" s="15">
+      <c r="P1" s="9">
         <v>2031</v>
       </c>
-      <c r="Q1" s="16">
+      <c r="Q1">
         <v>2032</v>
       </c>
-      <c r="R1" s="15">
+      <c r="R1" s="9">
         <v>2033</v>
       </c>
-      <c r="S1" s="16">
+      <c r="S1">
         <v>2034</v>
       </c>
-      <c r="T1" s="15">
+      <c r="T1" s="9">
         <v>2035</v>
       </c>
-      <c r="U1" s="16">
+      <c r="U1">
         <v>2036</v>
       </c>
-      <c r="V1" s="15">
+      <c r="V1" s="9">
         <v>2037</v>
       </c>
-      <c r="W1" s="16">
+      <c r="W1">
         <v>2038</v>
       </c>
-      <c r="X1" s="15">
+      <c r="X1" s="9">
         <v>2039</v>
       </c>
-      <c r="Y1" s="16">
+      <c r="Y1">
         <v>2040</v>
       </c>
-      <c r="Z1" s="15">
+      <c r="Z1" s="9">
         <v>2041</v>
       </c>
-      <c r="AA1" s="16">
+      <c r="AA1">
         <v>2042</v>
       </c>
-      <c r="AB1" s="15">
+      <c r="AB1" s="9">
         <v>2043</v>
       </c>
-      <c r="AC1" s="16">
+      <c r="AC1">
         <v>2044</v>
       </c>
-      <c r="AD1" s="15">
+      <c r="AD1" s="9">
         <v>2045</v>
       </c>
-      <c r="AE1" s="16">
+      <c r="AE1">
         <v>2046</v>
       </c>
-      <c r="AF1" s="15">
+      <c r="AF1" s="9">
         <v>2047</v>
       </c>
-      <c r="AG1" s="16">
+      <c r="AG1">
         <v>2048</v>
       </c>
-      <c r="AH1" s="15">
+      <c r="AH1" s="9">
         <v>2049</v>
       </c>
-      <c r="AI1" s="16">
+      <c r="AI1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="17">
-        <f>HPEC!B2*'IEA Data'!$D$4*About!$A$57</f>
-        <v>1.0567979137212481E-7</v>
-      </c>
-      <c r="C2" s="17">
+      <c r="B2" s="11">
+        <f>HPEC!B2*'IEA Data'!$D$4</f>
+        <v>4.1280886594208218E-7</v>
+      </c>
+      <c r="C2" s="11">
         <f>HPEC!C2*'IEA Data'!$D$4</f>
-        <v>2.0529693249762705E-7</v>
-      </c>
-      <c r="D2" s="17">
+        <v>4.057523041311057E-7</v>
+      </c>
+      <c r="D2" s="11">
         <f>HPEC!D2*'IEA Data'!$D$4</f>
-        <v>2.0172655106288616E-7</v>
-      </c>
-      <c r="E2" s="17">
+        <v>3.9869574232013086E-7</v>
+      </c>
+      <c r="E2" s="11">
         <f>HPEC!E2*'IEA Data'!$D$4</f>
-        <v>1.9815616962814441E-7</v>
-      </c>
-      <c r="F2" s="17">
+        <v>3.9163918050915428E-7</v>
+      </c>
+      <c r="F2" s="11">
         <f>HPEC!F2*'IEA Data'!$D$4</f>
-        <v>1.9458578819340353E-7</v>
-      </c>
-      <c r="G2" s="17">
+        <v>3.8458261869817944E-7</v>
+      </c>
+      <c r="G2" s="11">
         <f>HPEC!G2*'IEA Data'!$D$4</f>
-        <v>1.9101540675866177E-7</v>
-      </c>
-      <c r="H2" s="17">
+        <v>3.7752605688720286E-7</v>
+      </c>
+      <c r="H2" s="11">
         <f>HPEC!H2*'IEA Data'!$D$4</f>
-        <v>1.8744502532392004E-7</v>
-      </c>
-      <c r="I2" s="17">
+        <v>3.7046949507622632E-7</v>
+      </c>
+      <c r="I2" s="11">
         <f>HPEC!I2*'IEA Data'!$D$4</f>
-        <v>1.8387464388917916E-7</v>
-      </c>
-      <c r="J2" s="17">
+        <v>3.6341293326525154E-7</v>
+      </c>
+      <c r="J2" s="11">
         <f>HPEC!J2*'IEA Data'!$D$4</f>
-        <v>1.8030426245443741E-7</v>
-      </c>
-      <c r="K2" s="17">
+        <v>3.5635637145427495E-7</v>
+      </c>
+      <c r="K2" s="11">
         <f>HPEC!K2*'IEA Data'!$D$4</f>
-        <v>1.7673388101969655E-7</v>
-      </c>
-      <c r="L2" s="17">
+        <v>3.4929980964330012E-7</v>
+      </c>
+      <c r="L2" s="11">
         <f>HPEC!L2*'IEA Data'!$D$4</f>
-        <v>1.7316349958495477E-7</v>
-      </c>
-      <c r="M2" s="17">
+        <v>3.4224324783232353E-7</v>
+      </c>
+      <c r="M2" s="11">
         <f>HPEC!M2*'IEA Data'!$D$4</f>
-        <v>1.6959311815021391E-7</v>
-      </c>
-      <c r="N2" s="17">
+        <v>3.3518668602134869E-7</v>
+      </c>
+      <c r="N2" s="11">
         <f>HPEC!N2*'IEA Data'!$D$4</f>
-        <v>1.6602273671547219E-7</v>
-      </c>
-      <c r="O2" s="17">
+        <v>3.2813012421037216E-7</v>
+      </c>
+      <c r="O2" s="11">
         <f>HPEC!O2*'IEA Data'!$D$4</f>
-        <v>1.6245235528073128E-7</v>
-      </c>
-      <c r="P2" s="17">
+        <v>3.2107356239939732E-7</v>
+      </c>
+      <c r="P2" s="11">
         <f>HPEC!P2*'IEA Data'!$D$4</f>
-        <v>1.5955142036500393E-7</v>
-      </c>
-      <c r="Q2" s="17">
+        <v>3.1534010592797952E-7</v>
+      </c>
+      <c r="Q2" s="11">
         <f>HPEC!Q2*'IEA Data'!$D$4</f>
-        <v>1.566504854492766E-7</v>
-      </c>
-      <c r="R2" s="17">
+        <v>3.0960664945656172E-7</v>
+      </c>
+      <c r="R2" s="11">
         <f>HPEC!R2*'IEA Data'!$D$4</f>
-        <v>1.5374955053354928E-7</v>
-      </c>
-      <c r="S2" s="17">
+        <v>3.0387319298514391E-7</v>
+      </c>
+      <c r="S2" s="11">
         <f>HPEC!S2*'IEA Data'!$D$4</f>
-        <v>1.5084861561782187E-7</v>
-      </c>
-      <c r="T2" s="17">
+        <v>2.9813973651372606E-7</v>
+      </c>
+      <c r="T2" s="11">
         <f>HPEC!T2*'IEA Data'!$D$4</f>
-        <v>1.4794768070209455E-7</v>
-      </c>
-      <c r="U2" s="17">
+        <v>2.9240628004230825E-7</v>
+      </c>
+      <c r="U2" s="11">
         <f>HPEC!U2*'IEA Data'!$D$4</f>
-        <v>1.4504674578636722E-7</v>
-      </c>
-      <c r="V2" s="17">
+        <v>2.8667282357089045E-7</v>
+      </c>
+      <c r="V2" s="11">
         <f>HPEC!V2*'IEA Data'!$D$4</f>
-        <v>1.4214581087063987E-7</v>
-      </c>
-      <c r="W2" s="17">
+        <v>2.8093936709947264E-7</v>
+      </c>
+      <c r="W2" s="11">
         <f>HPEC!W2*'IEA Data'!$D$4</f>
-        <v>1.3924487595491252E-7</v>
-      </c>
-      <c r="X2" s="17">
+        <v>2.7520591062805484E-7</v>
+      </c>
+      <c r="X2" s="11">
         <f>HPEC!X2*'IEA Data'!$D$4</f>
-        <v>1.3634394103918516E-7</v>
-      </c>
-      <c r="Y2" s="17">
+        <v>2.6947245415663704E-7</v>
+      </c>
+      <c r="Y2" s="11">
         <f>HPEC!Y2*'IEA Data'!$D$4</f>
-        <v>1.3344300612345784E-7</v>
-      </c>
-      <c r="Z2" s="17">
+        <v>2.6373899768521923E-7</v>
+      </c>
+      <c r="Z2" s="11">
         <f>HPEC!Z2*'IEA Data'!$D$4</f>
-        <v>1.3054207120773049E-7</v>
-      </c>
-      <c r="AA2" s="17">
+        <v>2.5800554121380138E-7</v>
+      </c>
+      <c r="AA2" s="11">
         <f>HPEC!AA2*'IEA Data'!$D$4</f>
-        <v>1.2764113629200314E-7</v>
-      </c>
-      <c r="AB2" s="17">
+        <v>2.5227208474238357E-7</v>
+      </c>
+      <c r="AB2" s="11">
         <f>HPEC!AB2*'IEA Data'!$D$4</f>
-        <v>1.2474020137627581E-7</v>
-      </c>
-      <c r="AC2" s="17">
+        <v>2.4653862827096577E-7</v>
+      </c>
+      <c r="AC2" s="11">
         <f>HPEC!AC2*'IEA Data'!$D$4</f>
-        <v>1.2183926646054846E-7</v>
-      </c>
-      <c r="AD2" s="17">
+        <v>2.4080517179954797E-7</v>
+      </c>
+      <c r="AD2" s="11">
         <f>HPEC!AD2*'IEA Data'!$D$4</f>
-        <v>1.1893833154482112E-7</v>
-      </c>
-      <c r="AE2" s="17">
+        <v>2.3507171532813019E-7</v>
+      </c>
+      <c r="AE2" s="11">
         <f>HPEC!AE2*'IEA Data'!$D$4</f>
-        <v>1.1603739662909377E-7</v>
-      </c>
-      <c r="AF2" s="17">
+        <v>2.2933825885671233E-7</v>
+      </c>
+      <c r="AF2" s="11">
         <f>HPEC!AF2*'IEA Data'!$D$4</f>
-        <v>1.131364617133664E-7</v>
-      </c>
-      <c r="AG2" s="17">
+        <v>2.2360480238529453E-7</v>
+      </c>
+      <c r="AG2" s="11">
         <f>HPEC!AG2*'IEA Data'!$D$4</f>
-        <v>1.1023552679763908E-7</v>
-      </c>
-      <c r="AH2" s="12">
+        <v>2.1787134591387672E-7</v>
+      </c>
+      <c r="AH2" s="11">
         <f>HPEC!AH2*'IEA Data'!$D$4</f>
-        <v>1.0733459188191174E-7</v>
-      </c>
-      <c r="AI2" s="12">
+        <v>2.1213788944245895E-7</v>
+      </c>
+      <c r="AI2" s="11">
         <f>HPEC!AI2*'IEA Data'!$D$4</f>
-        <v>1.0443365696618439E-7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A3" s="16" t="s">
+        <v>2.0640443297104109E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="17">
-        <f>HPEC!B3*'IEA Data'!$D$8*About!$A$57</f>
-        <v>3.348092353322799E-7</v>
-      </c>
-      <c r="C3" s="17">
+      <c r="B3" s="11">
+        <f>HPEC!B3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="C3" s="11">
         <f>HPEC!C3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="D3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="D3" s="11">
         <f>HPEC!D3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="E3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="E3" s="11">
         <f>HPEC!E3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="F3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="F3" s="11">
         <f>HPEC!F3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="G3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="G3" s="11">
         <f>HPEC!G3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="H3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="H3" s="11">
         <f>HPEC!H3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="I3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="I3" s="11">
         <f>HPEC!I3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="J3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="J3" s="11">
         <f>HPEC!J3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="K3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="K3" s="11">
         <f>HPEC!K3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="L3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="L3" s="11">
         <f>HPEC!L3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="M3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="M3" s="11">
         <f>HPEC!M3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="N3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="N3" s="11">
         <f>HPEC!N3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="O3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="O3" s="11">
         <f>HPEC!O3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="P3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="P3" s="11">
         <f>HPEC!P3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="Q3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="Q3" s="11">
         <f>HPEC!Q3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="R3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="R3" s="11">
         <f>HPEC!R3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="S3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="S3" s="11">
         <f>HPEC!S3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="T3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="T3" s="11">
         <f>HPEC!T3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="U3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="U3" s="11">
         <f>HPEC!U3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="V3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="V3" s="11">
         <f>HPEC!V3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="W3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="W3" s="11">
         <f>HPEC!W3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="X3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="X3" s="11">
         <f>HPEC!X3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="Y3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="Y3" s="11">
         <f>HPEC!Y3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="Z3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="Z3" s="11">
         <f>HPEC!Z3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AA3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AA3" s="11">
         <f>HPEC!AA3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AB3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AB3" s="11">
         <f>HPEC!AB3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AC3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AC3" s="11">
         <f>HPEC!AC3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AD3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AD3" s="11">
         <f>HPEC!AD3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AE3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AE3" s="11">
         <f>HPEC!AE3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AF3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AF3" s="11">
         <f>HPEC!AF3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AG3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AG3" s="11">
         <f>HPEC!AG3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AH3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AH3" s="11">
         <f>HPEC!AH3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-      <c r="AI3" s="17">
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AI3" s="11">
         <f>HPEC!AI3*'IEA Data'!$D$8</f>
-        <v>6.617225938435121E-7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A4" s="16" t="s">
+        <v>1.307839644173545E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="17">
-        <f>HPEC!B4*'IEA Data'!$D$12*About!$A$57</f>
-        <v>1.0450557146799009E-6</v>
-      </c>
-      <c r="C4" s="17">
+      <c r="B4" s="11">
+        <f>HPEC!B4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="C4" s="11">
         <f>HPEC!C4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="D4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="D4" s="11">
         <f>HPEC!D4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="E4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="E4" s="11">
         <f>HPEC!E4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="F4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="F4" s="11">
         <f>HPEC!F4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="G4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="G4" s="11">
         <f>HPEC!G4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="H4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="H4" s="11">
         <f>HPEC!H4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="I4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="I4" s="11">
         <f>HPEC!I4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="J4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="J4" s="11">
         <f>HPEC!J4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="K4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="K4" s="11">
         <f>HPEC!K4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="L4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="L4" s="11">
         <f>HPEC!L4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="M4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="M4" s="11">
         <f>HPEC!M4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="N4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="N4" s="11">
         <f>HPEC!N4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="O4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="O4" s="11">
         <f>HPEC!O4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="P4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="P4" s="11">
         <f>HPEC!P4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="Q4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="Q4" s="11">
         <f>HPEC!Q4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="R4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="R4" s="11">
         <f>HPEC!R4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="S4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="S4" s="11">
         <f>HPEC!S4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="T4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="T4" s="11">
         <f>HPEC!T4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="U4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="U4" s="11">
         <f>HPEC!U4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="V4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="V4" s="11">
         <f>HPEC!V4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="W4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="W4" s="11">
         <f>HPEC!W4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="X4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="X4" s="11">
         <f>HPEC!X4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="Y4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="Y4" s="11">
         <f>HPEC!Y4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="Z4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="Z4" s="11">
         <f>HPEC!Z4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AA4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AA4" s="11">
         <f>HPEC!AA4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AB4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AB4" s="11">
         <f>HPEC!AB4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AC4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AC4" s="11">
         <f>HPEC!AC4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AD4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AD4" s="11">
         <f>HPEC!AD4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AE4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AE4" s="11">
         <f>HPEC!AE4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AF4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AF4" s="11">
         <f>HPEC!AF4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AG4" s="17">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AG4" s="11">
         <f>HPEC!AG4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AH4" s="12">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AH4" s="11">
         <f>HPEC!AH4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AI4" s="12">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AI4" s="11">
         <f>HPEC!AI4*'IEA Data'!$D$12</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+        <v>4.0822210076494796E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>B4</f>
-        <v>1.0450557146799009E-6</v>
-      </c>
-      <c r="C5" s="12">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="C5" s="11">
         <f t="shared" ref="C5:AI5" si="0">C4</f>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="D5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="E5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="F5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="G5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="H5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="J5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="K5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="L5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="M5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="N5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="O5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="P5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="Q5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="R5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="S5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="T5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="U5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="V5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="W5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="X5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="Y5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="Z5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AA5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AB5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AC5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AD5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AE5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AF5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AG5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AH5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-      <c r="AI5" s="12">
-        <f t="shared" si="0"/>
-        <v>2.0654656599978688E-6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="D5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="E5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="F5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="H5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="I5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="J5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="K5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="L5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="M5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="N5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="O5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="P5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="Q5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="R5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="S5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="T5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="U5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="V5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="W5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="X5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="Z5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AA5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AB5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AC5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AD5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AE5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AF5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AG5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AH5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AI5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="11">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <f t="shared" ref="C6:AI6" si="1">$B6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P6" s="11">
+      <c r="P6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S6" s="11">
+      <c r="S6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T6" s="11">
+      <c r="T6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U6" s="11">
+      <c r="U6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V6" s="11">
+      <c r="V6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W6" s="11">
+      <c r="W6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X6" s="11">
+      <c r="X6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y6" s="11">
+      <c r="Y6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="11">
+      <c r="Z6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA6" s="11">
+      <c r="AA6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB6" s="11">
+      <c r="AB6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC6" s="11">
+      <c r="AC6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD6" s="11">
+      <c r="AD6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AE6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF6" s="11">
+      <c r="AF6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG6" s="11">
+      <c r="AG6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="11">
+      <c r="AH6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI6" s="11">
+      <c r="AI6">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="11">
+        <f>B2</f>
+        <v>4.1280886594208218E-7</v>
+      </c>
+      <c r="C7" s="11">
+        <f t="shared" ref="C7:AI7" si="2">C2</f>
+        <v>4.057523041311057E-7</v>
+      </c>
+      <c r="D7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.9869574232013086E-7</v>
+      </c>
+      <c r="E7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.9163918050915428E-7</v>
+      </c>
+      <c r="F7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.8458261869817944E-7</v>
+      </c>
+      <c r="G7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.7752605688720286E-7</v>
+      </c>
+      <c r="H7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.7046949507622632E-7</v>
+      </c>
+      <c r="I7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.6341293326525154E-7</v>
+      </c>
+      <c r="J7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.5635637145427495E-7</v>
+      </c>
+      <c r="K7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.4929980964330012E-7</v>
+      </c>
+      <c r="L7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.4224324783232353E-7</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.3518668602134869E-7</v>
+      </c>
+      <c r="N7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.2813012421037216E-7</v>
+      </c>
+      <c r="O7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.2107356239939732E-7</v>
+      </c>
+      <c r="P7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.1534010592797952E-7</v>
+      </c>
+      <c r="Q7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.0960664945656172E-7</v>
+      </c>
+      <c r="R7" s="11">
+        <f t="shared" si="2"/>
+        <v>3.0387319298514391E-7</v>
+      </c>
+      <c r="S7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.9813973651372606E-7</v>
+      </c>
+      <c r="T7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.9240628004230825E-7</v>
+      </c>
+      <c r="U7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.8667282357089045E-7</v>
+      </c>
+      <c r="V7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.8093936709947264E-7</v>
+      </c>
+      <c r="W7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.7520591062805484E-7</v>
+      </c>
+      <c r="X7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6947245415663704E-7</v>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.6373899768521923E-7</v>
+      </c>
+      <c r="Z7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.5800554121380138E-7</v>
+      </c>
+      <c r="AA7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.5227208474238357E-7</v>
+      </c>
+      <c r="AB7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.4653862827096577E-7</v>
+      </c>
+      <c r="AC7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.4080517179954797E-7</v>
+      </c>
+      <c r="AD7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.3507171532813019E-7</v>
+      </c>
+      <c r="AE7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.2933825885671233E-7</v>
+      </c>
+      <c r="AF7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.2360480238529453E-7</v>
+      </c>
+      <c r="AG7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.1787134591387672E-7</v>
+      </c>
+      <c r="AH7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.1213788944245895E-7</v>
+      </c>
+      <c r="AI7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.0640443297104109E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="11">
+        <f>B3</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="C8" s="11">
+        <f t="shared" ref="C8:AI8" si="3">C3</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="D8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="E8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="F8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="H8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="I8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="J8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="K8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="L8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="M8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="N8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="O8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="P8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="Q8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="R8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="S8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="T8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="U8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="V8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="W8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="X8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="Z8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AA8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AB8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AC8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AD8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AE8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AF8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AG8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AH8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AI8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
+++ b/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\hydgn\HPEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\hydgn\HPEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144CF766-F142-4FDB-B3C8-5736800C38EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06FFE47-8401-4153-B365-3B8D108180A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30315" yWindow="315" windowWidth="21630" windowHeight="13245" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -125,9 +125,6 @@
     <t>biomass gasification</t>
   </si>
   <si>
-    <t>thermochemical water splitting</t>
-  </si>
-  <si>
     <t>hours per year</t>
   </si>
   <si>
@@ -188,27 +185,6 @@
     <t>Page 7, Table 3</t>
   </si>
   <si>
-    <t>Thermochemical Water Splitting</t>
-  </si>
-  <si>
-    <t>This technology can utilize heat from solar thermal (e.g. mirror</t>
-  </si>
-  <si>
-    <t>collectors, etc.) or from nuclear plants.  Capital costs would</t>
-  </si>
-  <si>
-    <t>vary greatly depending on the technology used.</t>
-  </si>
-  <si>
-    <t>This technology isn't used in the U.S. version of the model,</t>
-  </si>
-  <si>
-    <t>is available for EPS adaptations for other regions or future</t>
-  </si>
-  <si>
-    <t>U.S. region dataset updates.</t>
-  </si>
-  <si>
     <t>2018 USD/2012 USD</t>
   </si>
   <si>
@@ -222,9 +198,6 @@
   </si>
   <si>
     <t>HPEC Hydrogen Production Equipment OpEx</t>
-  </si>
-  <si>
-    <t>so no costs are included here, but the subscript element</t>
   </si>
   <si>
     <t>In other words, this variable should contain the CapEx</t>
@@ -290,6 +263,33 @@
   </si>
   <si>
     <t>natural gas reforming with CCS</t>
+  </si>
+  <si>
+    <t>hydrocarbon partial oxidation</t>
+  </si>
+  <si>
+    <t>Partial Oxidation of Hydrocarbons</t>
+  </si>
+  <si>
+    <t>According to ICF, POx reactors are essentially equivalent to autothermal</t>
+  </si>
+  <si>
+    <t>reformers (ATRs) but without a catalyst bed. For lack of economic data,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we assume that the costs mirror those of ATRs, which, per ICF, </t>
+  </si>
+  <si>
+    <t>Robertson, Penshorn, and McCurdy</t>
+  </si>
+  <si>
+    <t>Comparing the costs of industrial hydrogen technologies</t>
+  </si>
+  <si>
+    <t>https://www.icf.com/insights/energy/comparing-costs-of-industrial-hydrogen-technologies</t>
+  </si>
+  <si>
+    <t>have ~15% lower capital costs and ~5% lower production costs than SMRs.</t>
   </si>
 </sst>
 </file>
@@ -679,23 +679,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="45.85546875" customWidth="1"/>
+    <col min="2" max="2" width="45.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -703,248 +703,254 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B37" s="7">
         <v>2014</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B39" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="8" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B48" s="7">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B50" r:id="rId3" xr:uid="{0EAF8239-1601-435F-A7F3-DCBE0357401E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="25.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="1" max="3" width="25.453125" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -964,7 +970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -984,7 +990,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>10</v>
       </c>
@@ -1001,7 +1007,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -1036,7 +1042,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -1073,7 +1079,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -1090,7 +1096,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>17</v>
@@ -1108,7 +1114,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1128,7 +1134,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>10</v>
       </c>
@@ -1145,7 +1151,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>17</v>
@@ -1180,8 +1186,8 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1203,31 +1209,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1">
         <f>24*365</f>
         <v>8760</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3412.14</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.91400000000000003</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1241,14 +1247,14 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B1" s="9">
         <v>2017</v>
@@ -1353,7 +1359,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1494,7 +1500,7 @@
         <v>1.3760295531402741E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1635,7 +1641,7 @@
         <v>2.7826375407947768E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1776,7 +1782,7 @@
         <v>8.1644420152989595E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1917,149 +1923,150 @@
         <v>8.1644420152989595E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="B6" s="11">
+        <f>B3*0.85</f>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:R6" si="20">$B6</f>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="D6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="E6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="F6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="G6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="H6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="I6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="J6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="K6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="L6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="M6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="N6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="O6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="P6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="Q6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="R6">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="S6">
         <f t="shared" ref="S6:AI6" si="21">$B6</f>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="T6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="U6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="V6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="W6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="X6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="Y6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="Z6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AA6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AB6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AC6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AD6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AE6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AF6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AG6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AH6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.3652419096755601E-5</v>
       </c>
       <c r="AI6">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+        <v>2.3652419096755601E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B7" s="11">
         <f>B2</f>
@@ -2198,9 +2205,9 @@
         <v>1.3760295531402741E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B8" s="11">
         <f>B3</f>
@@ -2350,14 +2357,14 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B1" s="9">
         <v>2017</v>
@@ -2462,7 +2469,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2603,7 +2610,7 @@
         <v>2.0640443297104109E-7</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2744,7 +2751,7 @@
         <v>1.307839644173545E-6</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -2885,7 +2892,7 @@
         <v>4.0822210076494796E-6</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3026,149 +3033,150 @@
         <v>4.0822210076494796E-6</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="B6" s="11">
+        <f>B3*0.95</f>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:AI6" si="1">$B6</f>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="D6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="F6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="G6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="L6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="M6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="O6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="P6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="Q6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="S6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="T6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="U6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="V6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="W6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="X6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="Y6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="Z6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AA6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AB6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AC6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AD6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AE6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AF6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AG6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AH6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.2424476619648677E-6</v>
       </c>
       <c r="AI6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+        <v>1.2424476619648677E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B7" s="11">
         <f>B2</f>
@@ -3307,9 +3315,9 @@
         <v>2.0640443297104109E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B8" s="11">
         <f>B3</f>

--- a/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
+++ b/InputData/hydgn/HPEC/Hydrogen Production Eqpt Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27618"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\hydgn\HPEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\hydgn\HPEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06FFE47-8401-4153-B365-3B8D108180A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{1A959F09-0FF8-43A3-8843-1BA27D643902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FD5D0D4-CCAE-42D7-BAE1-37AC4F5DC6D1}"/>
   <bookViews>
-    <workbookView xWindow="30315" yWindow="315" windowWidth="21630" windowHeight="13245" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="hours_per_year">'Conversion Factors'!$A$1</definedName>
     <definedName name="usd_year_conv">'Conversion Factors'!$A$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,66 +50,12 @@
     <t>HPEC Hydrogen Production Equipment CapEx</t>
   </si>
   <si>
+    <t>HPEC Hydrogen Production Equipment OpEx</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Today</t>
-  </si>
-  <si>
-    <t>Long Term</t>
-  </si>
-  <si>
-    <t>electrolysis</t>
-  </si>
-  <si>
-    <t>CAPEX</t>
-  </si>
-  <si>
-    <t>USD/kWe</t>
-  </si>
-  <si>
-    <t>Efficiency (LHV)</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Annual OPEX</t>
-  </si>
-  <si>
-    <t>% of CAPEX</t>
-  </si>
-  <si>
-    <t>Stack Lifetime</t>
-  </si>
-  <si>
-    <t>operating hours</t>
-  </si>
-  <si>
-    <t>natural gas reforming</t>
-  </si>
-  <si>
-    <t>Emission factor</t>
-  </si>
-  <si>
-    <t>kgCO2/kgH2</t>
-  </si>
-  <si>
-    <t>coal gasification</t>
-  </si>
-  <si>
-    <t>Mapped Year</t>
-  </si>
-  <si>
     <t>International Energy Agency</t>
   </si>
   <si>
@@ -122,15 +68,6 @@
     <t>Assumptions annex, Page 3</t>
   </si>
   <si>
-    <t>biomass gasification</t>
-  </si>
-  <si>
-    <t>hours per year</t>
-  </si>
-  <si>
-    <t>BTU/kWh</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -146,58 +83,7 @@
     <t>capacity to $ of CapEx using the $/kW conversion factor.</t>
   </si>
   <si>
-    <t>Biomass Gassification</t>
-  </si>
-  <si>
-    <t>We don't have data on biomass gasification to hydrogen</t>
-  </si>
-  <si>
-    <t>CapEx from the same source or in the same format as</t>
-  </si>
-  <si>
-    <t>we do for electrolysis, natural gas reforming, and coal</t>
-  </si>
-  <si>
-    <t>gasification.  However, the following source provides</t>
-  </si>
-  <si>
-    <t>an equation that shows biomass gassificaiton to have</t>
-  </si>
-  <si>
-    <t>extremely similar capital costs to coal gasification.</t>
-  </si>
-  <si>
-    <t>Accordingly, we use the coal gasification values</t>
-  </si>
-  <si>
-    <t>for biomass gasification.</t>
-  </si>
-  <si>
-    <t>Acar, Canan and Dincer, Ibrahim</t>
-  </si>
-  <si>
-    <t>Comparative assessment of hydrogen production methods from renewable and non-renewable sources</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.ijhydene.2013.10.060</t>
-  </si>
-  <si>
-    <t>Page 7, Table 3</t>
-  </si>
-  <si>
-    <t>2018 USD/2012 USD</t>
-  </si>
-  <si>
-    <t>Currency Year</t>
-  </si>
-  <si>
-    <t>We assume the currency year of the IEA report (published in 2019)</t>
-  </si>
-  <si>
-    <t>is 2018 USD.</t>
-  </si>
-  <si>
-    <t>HPEC Hydrogen Production Equipment OpEx</t>
+    <t>The costs entered in this variable should be for a 100% capacity factor.</t>
   </si>
   <si>
     <t>In other words, this variable should contain the CapEx</t>
@@ -247,56 +133,170 @@
     </r>
   </si>
   <si>
-    <t>The costs entered in this variable should be for a 100% capacity factor.</t>
-  </si>
-  <si>
     <t>The adjustment for actual capacity factor is handled inside Vensim.</t>
   </si>
   <si>
+    <t>Biomass Gassification</t>
+  </si>
+  <si>
+    <t>We don't have data on biomass gasification to hydrogen</t>
+  </si>
+  <si>
+    <t>CapEx from the same source or in the same format as</t>
+  </si>
+  <si>
+    <t>we do for electrolysis, natural gas reforming, and coal</t>
+  </si>
+  <si>
+    <t>gasification.  However, the following source provides</t>
+  </si>
+  <si>
+    <t>an equation that shows biomass gassificaiton to have</t>
+  </si>
+  <si>
+    <t>extremely similar capital costs to coal gasification.</t>
+  </si>
+  <si>
+    <t>Accordingly, we use the coal gasification values</t>
+  </si>
+  <si>
+    <t>for biomass gasification.</t>
+  </si>
+  <si>
+    <t>Acar, Canan and Dincer, Ibrahim</t>
+  </si>
+  <si>
+    <t>Comparative assessment of hydrogen production methods from renewable and non-renewable sources</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ijhydene.2013.10.060</t>
+  </si>
+  <si>
+    <t>Page 7, Table 3</t>
+  </si>
+  <si>
+    <t>Thermochemical Water Splitting</t>
+  </si>
+  <si>
+    <t>This technology can utilize heat from solar thermal (e.g. mirror</t>
+  </si>
+  <si>
+    <t>collectors, etc.) or from nuclear plants.  Capital costs would</t>
+  </si>
+  <si>
+    <t>vary greatly depending on the technology used.</t>
+  </si>
+  <si>
+    <t>This technology isn't used in the U.S. version of the model,</t>
+  </si>
+  <si>
+    <t>so no costs are included here, but the subscript element</t>
+  </si>
+  <si>
+    <t>is available for EPS adaptations for other regions or future</t>
+  </si>
+  <si>
+    <t>U.S. region dataset updates.</t>
+  </si>
+  <si>
+    <t>Currency Year</t>
+  </si>
+  <si>
+    <t>We assume the currency year of the IEA report (published in 2019)</t>
+  </si>
+  <si>
+    <t>is 2018 USD.</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>Long Term</t>
+  </si>
+  <si>
+    <t>electrolysis</t>
+  </si>
+  <si>
+    <t>CAPEX</t>
+  </si>
+  <si>
+    <t>USD/kWe</t>
+  </si>
+  <si>
+    <t>Efficiency (LHV)</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Annual OPEX</t>
+  </si>
+  <si>
+    <t>% of CAPEX</t>
+  </si>
+  <si>
+    <t>Stack Lifetime</t>
+  </si>
+  <si>
+    <t>operating hours</t>
+  </si>
+  <si>
+    <t>natural gas reforming</t>
+  </si>
+  <si>
+    <t>Emission factor</t>
+  </si>
+  <si>
+    <t>kgCO2/kgH2</t>
+  </si>
+  <si>
+    <t>coal gasification</t>
+  </si>
+  <si>
+    <t>Mapped Year</t>
+  </si>
+  <si>
+    <t>hours per year</t>
+  </si>
+  <si>
+    <t>BTU/kWh</t>
+  </si>
+  <si>
+    <t>2018 USD/2012 USD</t>
+  </si>
+  <si>
     <t>CapEx Cost ($/BTU)</t>
   </si>
   <si>
+    <t>biomass gasification</t>
+  </si>
+  <si>
+    <t>thermochemical water splitting</t>
+  </si>
+  <si>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
+  </si>
+  <si>
     <t>OpEx Cost ($/BTU)</t>
-  </si>
-  <si>
-    <t>electrolysis with guaranteed clean electricity</t>
-  </si>
-  <si>
-    <t>natural gas reforming with CCS</t>
-  </si>
-  <si>
-    <t>hydrocarbon partial oxidation</t>
-  </si>
-  <si>
-    <t>Partial Oxidation of Hydrocarbons</t>
-  </si>
-  <si>
-    <t>According to ICF, POx reactors are essentially equivalent to autothermal</t>
-  </si>
-  <si>
-    <t>reformers (ATRs) but without a catalyst bed. For lack of economic data,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">we assume that the costs mirror those of ATRs, which, per ICF, </t>
-  </si>
-  <si>
-    <t>Robertson, Penshorn, and McCurdy</t>
-  </si>
-  <si>
-    <t>Comparing the costs of industrial hydrogen technologies</t>
-  </si>
-  <si>
-    <t>https://www.icf.com/insights/energy/comparing-costs-of-industrial-hydrogen-technologies</t>
-  </si>
-  <si>
-    <t>have ~15% lower capital costs and ~5% lower production costs than SMRs.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -679,306 +679,300 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="45.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="8" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="36" spans="1:2">
+      <c r="B36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2">
       <c r="B37" s="7">
         <v>2014</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2">
       <c r="B38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B39" s="8" t="s">
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B40" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B47" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B48" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B49" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B50" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B39" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B50" r:id="rId3" xr:uid="{0EAF8239-1601-435F-A7F3-DCBE0357401E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="25.453125" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="1" max="3" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E1" s="3">
         <v>2030</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" thickTop="1">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D2">
         <v>900</v>
@@ -990,12 +984,12 @@
         <v>450</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D3" s="4">
         <v>0.64</v>
@@ -1007,12 +1001,12 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="D4" s="5">
         <v>1.4999999999999999E-2</v>
@@ -1024,13 +1018,13 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="15.75" thickBot="1">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D5" s="6">
         <v>95000</v>
@@ -1042,15 +1036,15 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="15.75" thickTop="1">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>910</v>
@@ -1062,12 +1056,12 @@
         <v>910</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D7" s="4">
         <v>0.76</v>
@@ -1079,12 +1073,12 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="D8" s="5">
         <v>4.7E-2</v>
@@ -1096,13 +1090,13 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="15.75" thickBot="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D9" s="6">
         <v>8.9</v>
@@ -1114,15 +1108,15 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.75" thickTop="1">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="D10">
         <v>2670</v>
@@ -1134,12 +1128,12 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D11" s="4">
         <v>0.6</v>
@@ -1151,12 +1145,12 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4">
         <v>0.05</v>
@@ -1168,13 +1162,13 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D13" s="6">
         <v>20.2</v>
@@ -1186,10 +1180,10 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="15.75" thickTop="1"/>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D15">
         <v>2017</v>
@@ -1209,31 +1203,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1">
         <f>24*365</f>
         <v>8760</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>3412.14</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>0.91400000000000003</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1246,15 +1240,15 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BC8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:55">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B1" s="9">
         <v>2017</v>
@@ -1358,10 +1352,70 @@
       <c r="AI1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ1">
+        <v>2051</v>
+      </c>
+      <c r="AK1">
+        <v>2052</v>
+      </c>
+      <c r="AL1">
+        <v>2053</v>
+      </c>
+      <c r="AM1">
+        <v>2054</v>
+      </c>
+      <c r="AN1">
+        <v>2055</v>
+      </c>
+      <c r="AO1">
+        <v>2056</v>
+      </c>
+      <c r="AP1">
+        <v>2057</v>
+      </c>
+      <c r="AQ1">
+        <v>2058</v>
+      </c>
+      <c r="AR1">
+        <v>2059</v>
+      </c>
+      <c r="AS1">
+        <v>2060</v>
+      </c>
+      <c r="AT1">
+        <v>2061</v>
+      </c>
+      <c r="AU1">
+        <v>2062</v>
+      </c>
+      <c r="AV1">
+        <v>2063</v>
+      </c>
+      <c r="AW1">
+        <v>2064</v>
+      </c>
+      <c r="AX1">
+        <v>2065</v>
+      </c>
+      <c r="AY1">
+        <v>2066</v>
+      </c>
+      <c r="AZ1">
+        <v>2067</v>
+      </c>
+      <c r="BA1">
+        <v>2068</v>
+      </c>
+      <c r="BB1">
+        <v>2069</v>
+      </c>
+      <c r="BC1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B2" s="11">
         <f>TREND('IEA Data'!$D2:$E2,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
@@ -1499,10 +1553,90 @@
         <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
         <v>1.3760295531402741E-5</v>
       </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AJ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.3378065099974888E-5</v>
+      </c>
+      <c r="AK2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AK$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.2995834668547033E-5</v>
+      </c>
+      <c r="AL2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AL$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.2613604237119181E-5</v>
+      </c>
+      <c r="AM2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AM$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.2231373805691325E-5</v>
+      </c>
+      <c r="AN2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AN$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.1849143374263472E-5</v>
+      </c>
+      <c r="AO2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AO$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.1466912942835617E-5</v>
+      </c>
+      <c r="AP2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AP$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.1084682511407765E-5</v>
+      </c>
+      <c r="AQ2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AQ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.070245207997991E-5</v>
+      </c>
+      <c r="AR2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AR$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>1.0320221648552058E-5</v>
+      </c>
+      <c r="AS2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AS$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>9.9379912171242015E-6</v>
+      </c>
+      <c r="AT2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AT$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>9.5557607856963488E-6</v>
+      </c>
+      <c r="AU2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AU$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>9.1735303542684943E-6</v>
+      </c>
+      <c r="AV2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AV$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.7912999228406416E-6</v>
+      </c>
+      <c r="AW2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AW$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.4090694914127855E-6</v>
+      </c>
+      <c r="AX2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AX$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.0268390599849327E-6</v>
+      </c>
+      <c r="AY2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AY$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>7.6446086285570783E-6</v>
+      </c>
+      <c r="AZ2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,AZ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>7.2623781971292247E-6</v>
+      </c>
+      <c r="BA2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,BA$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>6.8801477657013703E-6</v>
+      </c>
+      <c r="BB2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,BB$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>6.4979173342735167E-6</v>
+      </c>
+      <c r="BC2" s="11">
+        <f>TREND('IEA Data'!$E2:$F2,'IEA Data'!$E$15:$F$15,BC$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>6.1156869028456623E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="B3" s="11">
         <f>TREND('IEA Data'!$D6:$E6,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
@@ -1640,10 +1774,90 @@
         <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
         <v>2.7826375407947768E-5</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AJ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AK3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AK$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AL3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AL$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AM3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AM$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AN3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AN$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AO3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AO$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AP3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AP$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AQ3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AQ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AR3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AR$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AS3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AS$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AT3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AT$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AU3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AU$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AV3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AV$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AW3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AW$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AX3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AX$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AY3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AY$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AZ3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,AZ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="BA3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,BA$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="BB3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,BB$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="BC3" s="11">
+        <f>TREND('IEA Data'!$E6:$F6,'IEA Data'!$E$15:$F$15,BC$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>2.7826375407947768E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:55">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B4" s="11">
         <f>TREND('IEA Data'!$D10:$E10,'IEA Data'!$D$15:$E$15,B$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
@@ -1781,10 +1995,90 @@
         <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AI$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
         <v>8.1644420152989595E-5</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AJ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AK4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AK$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AL4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AL$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AM4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AM$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AN4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AN$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AO4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AO$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AP4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AP$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AQ4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AQ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AR4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AR$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AS4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AS$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AT4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AT$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AU4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AU$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AV4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AV$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AW4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AW$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AX4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AX$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AY4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AY$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AZ4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,AZ$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="BA4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,BA$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="BB4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,BB$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="BC4" s="11">
+        <f>TREND('IEA Data'!$E10:$F10,'IEA Data'!$E$15:$F$15,BC$1)/hours_per_year/btu_per_kwh*usd_year_conv</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:55">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="B5" s="11">
         <f>B4</f>
@@ -1919,161 +2213,320 @@
         <v>8.1644420152989595E-5</v>
       </c>
       <c r="AI5" s="11">
-        <f t="shared" ref="AI5" si="19">AI4</f>
-        <v>8.1644420152989595E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+        <f t="shared" ref="AI5:BC5" si="19">AI4</f>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AJ5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AK5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AL5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AM5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AN5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AO5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AP5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AQ5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AR5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AS5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AT5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AU5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AV5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AW5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AX5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AY5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="AZ5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="BA5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="BB5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+      <c r="BC5" s="11">
+        <f t="shared" si="19"/>
+        <v>8.1644420152989595E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:55">
       <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="11">
-        <f>B3*0.85</f>
-        <v>2.3652419096755601E-5</v>
+        <v>70</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
       </c>
       <c r="C6">
         <f t="shared" ref="C6:R6" si="20">$B6</f>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <f t="shared" si="20"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <f t="shared" ref="S6:AI6" si="21">$B6</f>
-        <v>2.3652419096755601E-5</v>
+        <f t="shared" ref="S6:BC6" si="21">$B6</f>
+        <v>0</v>
       </c>
       <c r="T6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="Y6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AF6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AG6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AH6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
+        <v>0</v>
       </c>
       <c r="AI6">
         <f t="shared" si="21"/>
-        <v>2.3652419096755601E-5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:55">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B7" s="11">
         <f>B2</f>
         <v>2.7520591062805481E-5</v>
       </c>
       <c r="C7" s="11">
-        <f t="shared" ref="C7:AI7" si="22">C2</f>
+        <f t="shared" ref="C7:BC7" si="22">C2</f>
         <v>2.7050153608740382E-5</v>
       </c>
       <c r="D7" s="11">
@@ -2204,17 +2657,97 @@
         <f t="shared" si="22"/>
         <v>1.3760295531402741E-5</v>
       </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.3378065099974888E-5</v>
+      </c>
+      <c r="AK7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.2995834668547033E-5</v>
+      </c>
+      <c r="AL7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.2613604237119181E-5</v>
+      </c>
+      <c r="AM7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.2231373805691325E-5</v>
+      </c>
+      <c r="AN7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.1849143374263472E-5</v>
+      </c>
+      <c r="AO7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.1466912942835617E-5</v>
+      </c>
+      <c r="AP7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.1084682511407765E-5</v>
+      </c>
+      <c r="AQ7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.070245207997991E-5</v>
+      </c>
+      <c r="AR7" s="11">
+        <f t="shared" si="22"/>
+        <v>1.0320221648552058E-5</v>
+      </c>
+      <c r="AS7" s="11">
+        <f t="shared" si="22"/>
+        <v>9.9379912171242015E-6</v>
+      </c>
+      <c r="AT7" s="11">
+        <f t="shared" si="22"/>
+        <v>9.5557607856963488E-6</v>
+      </c>
+      <c r="AU7" s="11">
+        <f t="shared" si="22"/>
+        <v>9.1735303542684943E-6</v>
+      </c>
+      <c r="AV7" s="11">
+        <f t="shared" si="22"/>
+        <v>8.7912999228406416E-6</v>
+      </c>
+      <c r="AW7" s="11">
+        <f t="shared" si="22"/>
+        <v>8.4090694914127855E-6</v>
+      </c>
+      <c r="AX7" s="11">
+        <f t="shared" si="22"/>
+        <v>8.0268390599849327E-6</v>
+      </c>
+      <c r="AY7" s="11">
+        <f t="shared" si="22"/>
+        <v>7.6446086285570783E-6</v>
+      </c>
+      <c r="AZ7" s="11">
+        <f t="shared" si="22"/>
+        <v>7.2623781971292247E-6</v>
+      </c>
+      <c r="BA7" s="11">
+        <f t="shared" si="22"/>
+        <v>6.8801477657013703E-6</v>
+      </c>
+      <c r="BB7" s="11">
+        <f t="shared" si="22"/>
+        <v>6.4979173342735167E-6</v>
+      </c>
+      <c r="BC7" s="11">
+        <f t="shared" si="22"/>
+        <v>6.1156869028456623E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:55">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B8" s="11">
         <f>B3</f>
         <v>2.7826375407947768E-5</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:AI8" si="23">C3</f>
+        <f t="shared" ref="C8:BC8" si="23">C3</f>
         <v>2.7826375407947768E-5</v>
       </c>
       <c r="D8" s="11">
@@ -2342,6 +2875,86 @@
         <v>2.7826375407947768E-5</v>
       </c>
       <c r="AI8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AJ8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AK8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AL8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AM8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AN8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AO8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AP8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AQ8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AR8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AS8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AT8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AU8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AV8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AW8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AX8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AY8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="AZ8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="BA8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="BB8" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7826375407947768E-5</v>
+      </c>
+      <c r="BC8" s="11">
         <f t="shared" si="23"/>
         <v>2.7826375407947768E-5</v>
       </c>
@@ -2356,15 +2969,15 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BD8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:56">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B1" s="9">
         <v>2017</v>
@@ -2468,10 +3081,70 @@
       <c r="AI1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ1">
+        <v>2051</v>
+      </c>
+      <c r="AK1">
+        <v>2052</v>
+      </c>
+      <c r="AL1">
+        <v>2053</v>
+      </c>
+      <c r="AM1">
+        <v>2054</v>
+      </c>
+      <c r="AN1">
+        <v>2055</v>
+      </c>
+      <c r="AO1">
+        <v>2056</v>
+      </c>
+      <c r="AP1">
+        <v>2057</v>
+      </c>
+      <c r="AQ1">
+        <v>2058</v>
+      </c>
+      <c r="AR1">
+        <v>2059</v>
+      </c>
+      <c r="AS1">
+        <v>2060</v>
+      </c>
+      <c r="AT1">
+        <v>2061</v>
+      </c>
+      <c r="AU1">
+        <v>2062</v>
+      </c>
+      <c r="AV1">
+        <v>2063</v>
+      </c>
+      <c r="AW1">
+        <v>2064</v>
+      </c>
+      <c r="AX1">
+        <v>2065</v>
+      </c>
+      <c r="AY1">
+        <v>2066</v>
+      </c>
+      <c r="AZ1">
+        <v>2067</v>
+      </c>
+      <c r="BA1">
+        <v>2068</v>
+      </c>
+      <c r="BB1">
+        <v>2069</v>
+      </c>
+      <c r="BC1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:56">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B2" s="11">
         <f>HPEC!B2*'IEA Data'!$D$4</f>
@@ -2609,10 +3282,90 @@
         <f>HPEC!AI2*'IEA Data'!$D$4</f>
         <v>2.0640443297104109E-7</v>
       </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ2" s="11">
+        <f>HPEC!AJ2*'IEA Data'!$D$4</f>
+        <v>2.0067097649962331E-7</v>
+      </c>
+      <c r="AK2" s="11">
+        <f>HPEC!AK2*'IEA Data'!$D$4</f>
+        <v>1.9493752002820548E-7</v>
+      </c>
+      <c r="AL2" s="11">
+        <f>HPEC!AL2*'IEA Data'!$D$4</f>
+        <v>1.8920406355678771E-7</v>
+      </c>
+      <c r="AM2" s="11">
+        <f>HPEC!AM2*'IEA Data'!$D$4</f>
+        <v>1.8347060708536988E-7</v>
+      </c>
+      <c r="AN2" s="11">
+        <f>HPEC!AN2*'IEA Data'!$D$4</f>
+        <v>1.7773715061395207E-7</v>
+      </c>
+      <c r="AO2" s="11">
+        <f>HPEC!AO2*'IEA Data'!$D$4</f>
+        <v>1.7200369414253427E-7</v>
+      </c>
+      <c r="AP2" s="11">
+        <f>HPEC!AP2*'IEA Data'!$D$4</f>
+        <v>1.6627023767111646E-7</v>
+      </c>
+      <c r="AQ2" s="11">
+        <f>HPEC!AQ2*'IEA Data'!$D$4</f>
+        <v>1.6053678119969866E-7</v>
+      </c>
+      <c r="AR2" s="11">
+        <f>HPEC!AR2*'IEA Data'!$D$4</f>
+        <v>1.5480332472828086E-7</v>
+      </c>
+      <c r="AS2" s="11">
+        <f>HPEC!AS2*'IEA Data'!$D$4</f>
+        <v>1.4906986825686303E-7</v>
+      </c>
+      <c r="AT2" s="11">
+        <f>HPEC!AT2*'IEA Data'!$D$4</f>
+        <v>1.4333641178544522E-7</v>
+      </c>
+      <c r="AU2" s="11">
+        <f>HPEC!AU2*'IEA Data'!$D$4</f>
+        <v>1.3760295531402742E-7</v>
+      </c>
+      <c r="AV2" s="11">
+        <f>HPEC!AV2*'IEA Data'!$D$4</f>
+        <v>1.3186949884260962E-7</v>
+      </c>
+      <c r="AW2" s="11">
+        <f>HPEC!AW2*'IEA Data'!$D$4</f>
+        <v>1.2613604237119179E-7</v>
+      </c>
+      <c r="AX2" s="11">
+        <f>HPEC!AX2*'IEA Data'!$D$4</f>
+        <v>1.2040258589977398E-7</v>
+      </c>
+      <c r="AY2" s="11">
+        <f>HPEC!AY2*'IEA Data'!$D$4</f>
+        <v>1.1466912942835617E-7</v>
+      </c>
+      <c r="AZ2" s="11">
+        <f>HPEC!AZ2*'IEA Data'!$D$4</f>
+        <v>1.0893567295693836E-7</v>
+      </c>
+      <c r="BA2" s="11">
+        <f>HPEC!BA2*'IEA Data'!$D$4</f>
+        <v>1.0320221648552055E-7</v>
+      </c>
+      <c r="BB2" s="11">
+        <f>HPEC!BB2*'IEA Data'!$D$4</f>
+        <v>9.7468760014102742E-8</v>
+      </c>
+      <c r="BC2" s="11">
+        <f>HPEC!BC2*'IEA Data'!$D$4</f>
+        <v>9.1735303542684938E-8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:56">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="B3" s="11">
         <f>HPEC!B3*'IEA Data'!$D$8</f>
@@ -2750,10 +3503,90 @@
         <f>HPEC!AI3*'IEA Data'!$D$8</f>
         <v>1.307839644173545E-6</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ3" s="11">
+        <f>HPEC!AJ3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AK3" s="11">
+        <f>HPEC!AK3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AL3" s="11">
+        <f>HPEC!AL3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AM3" s="11">
+        <f>HPEC!AM3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AN3" s="11">
+        <f>HPEC!AN3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AO3" s="11">
+        <f>HPEC!AO3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AP3" s="11">
+        <f>HPEC!AP3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AQ3" s="11">
+        <f>HPEC!AQ3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AR3" s="11">
+        <f>HPEC!AR3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AS3" s="11">
+        <f>HPEC!AS3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AT3" s="11">
+        <f>HPEC!AT3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AU3" s="11">
+        <f>HPEC!AU3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AV3" s="11">
+        <f>HPEC!AV3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AW3" s="11">
+        <f>HPEC!AW3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AX3" s="11">
+        <f>HPEC!AX3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AY3" s="11">
+        <f>HPEC!AY3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AZ3" s="11">
+        <f>HPEC!AZ3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="BA3" s="11">
+        <f>HPEC!BA3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="BB3" s="11">
+        <f>HPEC!BB3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="BC3" s="11">
+        <f>HPEC!BC3*'IEA Data'!$D$8</f>
+        <v>1.307839644173545E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:56">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B4" s="11">
         <f>HPEC!B4*'IEA Data'!$D$12</f>
@@ -2891,17 +3724,97 @@
         <f>HPEC!AI4*'IEA Data'!$D$12</f>
         <v>4.0822210076494796E-6</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ4" s="11">
+        <f>HPEC!AJ4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AK4" s="11">
+        <f>HPEC!AK4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AL4" s="11">
+        <f>HPEC!AL4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AM4" s="11">
+        <f>HPEC!AM4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AN4" s="11">
+        <f>HPEC!AN4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AO4" s="11">
+        <f>HPEC!AO4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AP4" s="11">
+        <f>HPEC!AP4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AQ4" s="11">
+        <f>HPEC!AQ4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AR4" s="11">
+        <f>HPEC!AR4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AS4" s="11">
+        <f>HPEC!AS4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AT4" s="11">
+        <f>HPEC!AT4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AU4" s="11">
+        <f>HPEC!AU4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AV4" s="11">
+        <f>HPEC!AV4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AW4" s="11">
+        <f>HPEC!AW4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AX4" s="11">
+        <f>HPEC!AX4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AY4" s="11">
+        <f>HPEC!AY4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AZ4" s="11">
+        <f>HPEC!AZ4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="BA4" s="11">
+        <f>HPEC!BA4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="BB4" s="11">
+        <f>HPEC!BB4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="BC4" s="11">
+        <f>HPEC!BC4*'IEA Data'!$D$12</f>
+        <v>4.0822210076494796E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:56">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="B5" s="11">
         <f>B4</f>
         <v>4.0822210076494796E-6</v>
       </c>
       <c r="C5" s="11">
-        <f t="shared" ref="C5:AI5" si="0">C4</f>
+        <f t="shared" ref="C5:BD5" si="0">C4</f>
         <v>4.0822210076494796E-6</v>
       </c>
       <c r="D5" s="11">
@@ -3032,158 +3945,318 @@
         <f t="shared" si="0"/>
         <v>4.0822210076494796E-6</v>
       </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AK5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AL5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AM5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AN5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AO5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AP5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AQ5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AR5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AS5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AT5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AU5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AV5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AW5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AX5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AY5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="AZ5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="BA5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="BB5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="BC5" s="11">
+        <f t="shared" si="0"/>
+        <v>4.0822210076494796E-6</v>
+      </c>
+      <c r="BD5" s="11"/>
+    </row>
+    <row r="6" spans="1:56">
       <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="11">
-        <f>B3*0.95</f>
-        <v>1.2424476619648677E-6</v>
+        <v>70</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:AI6" si="1">$B6</f>
-        <v>1.2424476619648677E-6</v>
+        <f t="shared" ref="C6:BC6" si="1">$B6</f>
+        <v>0</v>
       </c>
       <c r="D6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="T6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="V6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="W6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="Y6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AB6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AD6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AF6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AG6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AH6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
+        <v>0</v>
       </c>
       <c r="AI6">
         <f t="shared" si="1"/>
-        <v>1.2424476619648677E-6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:56">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B7" s="11">
         <f>B2</f>
         <v>4.1280886594208218E-7</v>
       </c>
       <c r="C7" s="11">
-        <f t="shared" ref="C7:AI7" si="2">C2</f>
+        <f t="shared" ref="C7:BD7" si="2">C2</f>
         <v>4.057523041311057E-7</v>
       </c>
       <c r="D7" s="11">
@@ -3314,17 +4387,98 @@
         <f t="shared" si="2"/>
         <v>2.0640443297104109E-7</v>
       </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="AJ7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.0067097649962331E-7</v>
+      </c>
+      <c r="AK7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.9493752002820548E-7</v>
+      </c>
+      <c r="AL7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8920406355678771E-7</v>
+      </c>
+      <c r="AM7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.8347060708536988E-7</v>
+      </c>
+      <c r="AN7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.7773715061395207E-7</v>
+      </c>
+      <c r="AO7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.7200369414253427E-7</v>
+      </c>
+      <c r="AP7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.6627023767111646E-7</v>
+      </c>
+      <c r="AQ7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.6053678119969866E-7</v>
+      </c>
+      <c r="AR7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.5480332472828086E-7</v>
+      </c>
+      <c r="AS7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.4906986825686303E-7</v>
+      </c>
+      <c r="AT7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.4333641178544522E-7</v>
+      </c>
+      <c r="AU7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.3760295531402742E-7</v>
+      </c>
+      <c r="AV7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.3186949884260962E-7</v>
+      </c>
+      <c r="AW7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.2613604237119179E-7</v>
+      </c>
+      <c r="AX7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.2040258589977398E-7</v>
+      </c>
+      <c r="AY7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.1466912942835617E-7</v>
+      </c>
+      <c r="AZ7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0893567295693836E-7</v>
+      </c>
+      <c r="BA7" s="11">
+        <f t="shared" si="2"/>
+        <v>1.0320221648552055E-7</v>
+      </c>
+      <c r="BB7" s="11">
+        <f t="shared" si="2"/>
+        <v>9.7468760014102742E-8</v>
+      </c>
+      <c r="BC7" s="11">
+        <f t="shared" si="2"/>
+        <v>9.1735303542684938E-8</v>
+      </c>
+      <c r="BD7" s="11"/>
+    </row>
+    <row r="8" spans="1:56">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B8" s="11">
         <f>B3</f>
         <v>1.307839644173545E-6</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" ref="C8:AI8" si="3">C3</f>
+        <f t="shared" ref="C8:BC8" si="3">C3</f>
         <v>1.307839644173545E-6</v>
       </c>
       <c r="D8" s="11">
@@ -3452,6 +4606,86 @@
         <v>1.307839644173545E-6</v>
       </c>
       <c r="AI8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AJ8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AK8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AL8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AM8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AN8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AO8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AP8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AQ8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AR8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AS8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AT8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AU8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AV8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AW8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AX8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AY8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="AZ8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="BA8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="BB8" s="11">
+        <f t="shared" si="3"/>
+        <v>1.307839644173545E-6</v>
+      </c>
+      <c r="BC8" s="11">
         <f t="shared" si="3"/>
         <v>1.307839644173545E-6</v>
       </c>
@@ -3459,4 +4693,165 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD45F44D-A410-47EB-8C40-6B8AB71CDD81}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F64F8C89-F1A3-41A3-BC18-32628D9D1FDD}"/>
 </file>